--- a/Handling-timeIT.xlsx
+++ b/Handling-timeIT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanignaciomartinez/Desktop/StockAmazon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A0F3B9A-032F-A34B-A60F-4143DB851690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61422BA1-96C1-F04E-8820-9DDF4B51D331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{D9964971-FD87-6A4B-96D8-DE1421DA450B}"/>
   </bookViews>
@@ -478,7 +478,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
